--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hudson Lynam\Documents\websites\csc110-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8993D5E6-6BAC-40CC-BDF5-8886EBD2D30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C677B52-33F6-4B10-A791-34AE98D463E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8E2BECA6-270F-C740-9ED5-1344B6EDB180}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8E2BECA6-270F-C740-9ED5-1344B6EDB180}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="81">
   <si>
     <t>week_start</t>
   </si>
@@ -273,6 +273,12 @@
   </si>
   <si>
     <t xml:space="preserve">March 9-16, 2026 </t>
+  </si>
+  <si>
+    <t>fall 2026</t>
+  </si>
+  <si>
+    <t>3:30pm - 5:30pm</t>
   </si>
 </sst>
 </file>
@@ -660,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFD2179-9860-BE4A-AB2A-CF760AB84B2E}">
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -2730,8 +2736,316 @@
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C116" s="1"/>
-      <c r="E116" s="5"/>
+      <c r="A116" t="s">
+        <v>79</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46258</v>
+      </c>
+      <c r="H116" t="s">
+        <v>45</v>
+      </c>
+      <c r="I116" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>79</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117" s="1">
+        <v>46265</v>
+      </c>
+      <c r="F117" s="6"/>
+      <c r="H117" t="s">
+        <v>46</v>
+      </c>
+      <c r="I117" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>79</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118" s="1">
+        <v>46272</v>
+      </c>
+      <c r="E118" s="5">
+        <v>46272</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" t="s">
+        <v>47</v>
+      </c>
+      <c r="I118" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>79</v>
+      </c>
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46279</v>
+      </c>
+      <c r="H119" t="s">
+        <v>48</v>
+      </c>
+      <c r="I119" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>79</v>
+      </c>
+      <c r="B120">
+        <v>5</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46286</v>
+      </c>
+      <c r="H120" t="s">
+        <v>49</v>
+      </c>
+      <c r="I120" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>79</v>
+      </c>
+      <c r="B121">
+        <v>6</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46293</v>
+      </c>
+      <c r="H121" t="s">
+        <v>50</v>
+      </c>
+      <c r="I121" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>79</v>
+      </c>
+      <c r="B122">
+        <v>7</v>
+      </c>
+      <c r="C122" s="1">
+        <v>46300</v>
+      </c>
+      <c r="D122" t="s">
+        <v>2</v>
+      </c>
+      <c r="E122" s="1">
+        <v>46302</v>
+      </c>
+      <c r="H122" t="s">
+        <v>51</v>
+      </c>
+      <c r="I122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>79</v>
+      </c>
+      <c r="B123">
+        <v>8</v>
+      </c>
+      <c r="C123" s="1">
+        <v>46307</v>
+      </c>
+      <c r="H123" t="s">
+        <v>52</v>
+      </c>
+      <c r="I123" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>79</v>
+      </c>
+      <c r="B124">
+        <v>9</v>
+      </c>
+      <c r="C124" s="1">
+        <v>46314</v>
+      </c>
+      <c r="H124" t="s">
+        <v>53</v>
+      </c>
+      <c r="I124" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>79</v>
+      </c>
+      <c r="B125">
+        <v>10</v>
+      </c>
+      <c r="C125" s="1">
+        <v>46321</v>
+      </c>
+      <c r="H125" t="s">
+        <v>54</v>
+      </c>
+      <c r="I125" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>79</v>
+      </c>
+      <c r="B126">
+        <v>11</v>
+      </c>
+      <c r="C126" s="1">
+        <v>46328</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E126" s="1">
+        <v>46330</v>
+      </c>
+      <c r="H126" t="s">
+        <v>55</v>
+      </c>
+      <c r="I126" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>79</v>
+      </c>
+      <c r="B127">
+        <v>12</v>
+      </c>
+      <c r="C127" s="1">
+        <v>46335</v>
+      </c>
+      <c r="E127" s="3">
+        <v>45972</v>
+      </c>
+      <c r="G127" t="s">
+        <v>14</v>
+      </c>
+      <c r="H127" t="s">
+        <v>56</v>
+      </c>
+      <c r="I127" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>79</v>
+      </c>
+      <c r="B128">
+        <v>13</v>
+      </c>
+      <c r="C128" s="1">
+        <v>46342</v>
+      </c>
+      <c r="H128" t="s">
+        <v>57</v>
+      </c>
+      <c r="I128" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>79</v>
+      </c>
+      <c r="B129">
+        <v>14</v>
+      </c>
+      <c r="C129" s="1">
+        <v>46349</v>
+      </c>
+      <c r="E129" s="3">
+        <v>45987</v>
+      </c>
+      <c r="G129" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" t="s">
+        <v>58</v>
+      </c>
+      <c r="I129" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>79</v>
+      </c>
+      <c r="B130">
+        <v>15</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46356</v>
+      </c>
+      <c r="H130" t="s">
+        <v>59</v>
+      </c>
+      <c r="I130" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>79</v>
+      </c>
+      <c r="B131">
+        <v>16</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46363</v>
+      </c>
+      <c r="D131" t="s">
+        <v>6</v>
+      </c>
+      <c r="E131" s="1">
+        <v>46002</v>
+      </c>
+      <c r="F131" t="s">
+        <v>80</v>
+      </c>
+      <c r="H131" t="s">
+        <v>65</v>
+      </c>
+      <c r="I131" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
